--- a/hardware/expansion-board-v4/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v4/BOM_采购清单.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12pF</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -895,24 +895,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C0G/NP0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>50V</t>
-        </is>
-      </c>
+          <t>X5R</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>50</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0603 10uF 16V X5R</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>建议 C0G（X7R 可用，需实测频偏）</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,7 +918,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15pF</t>
+          <t>12pF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -959,7 +955,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1nF</t>
+          <t>15pF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -969,7 +965,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>不限</t>
+          <t>C0G/NP0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -982,7 +978,11 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>建议 C0G（X7R 可用，需实测频偏）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>1nF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>X5R</t>
+          <t>不限</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25V</t>
+          <t>50V</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200pF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>不限</t>
+          <t>X5R</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>50V</t>
+          <t>25V</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3pF</t>
+          <t>200pF</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>3pF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1101,27 +1101,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>X5R</t>
+          <t>不限</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16V</t>
+          <t>50V</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>50</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Samsung CL10A475KO8NNNC</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>C19666</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1132,12 +1124,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10uF</t>
+          <t>4.7uF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1147,14 +1139,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25V</t>
+          <t>16V</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>50</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Samsung CL10A475KO8NNNC</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>C19666</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1165,119 +1165,127 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22uF</t>
+          <t>47nF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>X5R</t>
+          <t>X7R</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16V</t>
+          <t>50V</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>50</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0603 47nF 25V X7R</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>电阻</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>6.8uF</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>X5R</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>100</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0603 6.8uF 25V X5R</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>精度 ±1%</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>电阻</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>52.3R</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>X5R</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>25V</t>
+        </is>
+      </c>
       <c r="F22" t="n">
-        <v>100</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>YAGEO RC0402FR-0752R3L ±1%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>C273696</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>精度 ±1%</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>电阻</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0R</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>不限</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>X5R</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>16V</t>
+        </is>
+      </c>
       <c r="F23" t="n">
         <v>50</v>
       </c>
@@ -1288,25 +1296,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>电阻</t>
+          <t>电容</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>X5R</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
         <v>50</v>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1206 22uF 10V X5R</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
     </row>
@@ -1318,22 +1334,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>精度 ±1%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1343,22 +1363,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18k</t>
+          <t>52.3R</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>50</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>YAGEO RC0402FR-0752R3L ±1%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>C273696</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>精度 ±1%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1368,7 +1400,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1376,7 +1408,11 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
         <v>50</v>
@@ -1393,7 +1429,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27R</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1418,7 +1454,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1443,7 +1479,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5.1k</t>
+          <t>150k</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1456,424 +1492,867 @@
       <c r="F30" t="n">
         <v>50</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0603 150k 1%</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>电感</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>180R</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>绕线</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DDY WI0402IFR10KST-HF</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>C18221115</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
-        </is>
-      </c>
+          <t>0603 180R 1%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>电感</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27nH</t>
+          <t>18k</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>绕线</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>100</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>muRata LQW15AN27NG0ZD</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>C7519921</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>电感</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>绕线</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>100</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>APV AHW1005C-33NJTF</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>C6807986</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>电感</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>27R</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>绕线</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>100</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>muRata LQW15AN6N8G00D</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>C82919</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>电感</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>31.6k</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>绕线</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>muRata LQW15AN7N5G00D</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>C82918</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
-        </is>
-      </c>
+          <t>0603 31.6k 1%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>电感</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.8uH</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>不限</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>50</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>TDK MLZ2012N6R8LT000</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>C82157</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>二极管</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ESD 3.3V/0.6pF</t>
+          <t>470k</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>C2830293</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>低结电容 ESD 管（≤0.6pF）</t>
-        </is>
-      </c>
+          <t>0603 470k 1%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>二极管</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B5819W</t>
+          <t>5.62k</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SOD-123</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>JSMSEMI 1N5819W</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>C963381</t>
-        </is>
-      </c>
+          <t>0603 5.62k 1%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>保险丝</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>6.8k</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>金瑞 JK-SMD0805-020-30V</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>C516070</t>
-        </is>
-      </c>
+          <t>0603 6.8k 1%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>三极管/MOS</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SOT-23</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UMW AO3401A</t>
+          <t>DDY WI0402IFR10KST-HF</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C347476</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
+          <t>C18221115</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>27nH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SOT-363/SC-70-6</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>muRata LQW15AN27NG0ZD</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>C7519921</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>电感</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>33nH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>APV AHW1005C-33NJTF</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>C6807986</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>电感</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>6.8nH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>muRata LQW15AN6N8G00D</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>C82919</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>电感</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7.5nH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>muRata LQW15AN7N5G00D</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>C82918</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>电感</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>6.8uH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>50</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>TDK MLZ2012N6R8LT000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>C82157</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>电感</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1.5uH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>L_Bourns-SRN4018</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.5uH SRN4018 Isat&gt;=4A</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>电感</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1uH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>L_Bourns-SRN4018</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1uH SRN4018 Isat&gt;=5A</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>二极管</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ESD 3.3V/0.6pF</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
         <v>4</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>C2830293</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>低结电容 ESD 管（≤0.6pF）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>保险丝</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6V/200mA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>金瑞 JK-SMD0805-020-30V</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>C516070</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>三极管/MOS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>6</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>UMW AO3401A</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>C347476</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>三极管/MOS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SY7069</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SY7069ADC</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>淘宝（立创未见）</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>XA17-G4K</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SOT-363/SC-70-6</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>信路达 XA17-G4K</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>C513494</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CH224K</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CH224K_ESSOP-10</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>C970725</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MX1.25WT-2P BAT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>MX1.25 卧贴 1.25WT-2P</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>103AT-2 10k NTC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NTC_103AT-2_Leaded_P2.54mm</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>103AT-2 10k NTC B=3435</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SY6970</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SY6970QCC</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>C5357542</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hardware/expansion-board-v4/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v4/BOM_采购清单.xlsx
@@ -1748,43 +1748,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>电感</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>NCP18XH103F03RB 10k NTC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>绕线</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DDY WI0402IFR10KST-HF</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>C18221115</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>必须绕线电感，叠层款不行</t>
-        </is>
-      </c>
+          <t>Murata NCP18XH103F03RB / TDK NTCG163JF103FT1 / 国产 0603 10K 1%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1794,7 +1782,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>27nH</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1813,12 +1801,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>muRata LQW15AN27NG0ZD</t>
+          <t>DDY WI0402IFR10KST-HF</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C7519921</t>
+          <t>C18221115</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1835,7 +1823,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>27nH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1854,12 +1842,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>APV AHW1005C-33NJTF</t>
+          <t>muRata LQW15AN27NG0ZD</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C6807986</t>
+          <t>C7519921</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1876,7 +1864,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1895,12 +1883,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>muRata LQW15AN6N8G00D</t>
+          <t>APV AHW1005C-33NJTF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C82919</t>
+          <t>C6807986</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1917,7 +1905,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>6.8nH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1936,12 +1924,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>muRata LQW15AN7N5G00D</t>
+          <t>muRata LQW15AN6N8G00D</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C82918</t>
+          <t>C82919</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1958,36 +1946,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6.8uH</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>不限</t>
+          <t>绕线</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TDK MLZ2012N6R8LT000</t>
+          <t>muRata LQW15AN7N5G00D</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>C82157</t>
+          <t>C82918</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
+          <t>必须绕线电感，叠层款不行</t>
         </is>
       </c>
     </row>
@@ -1999,12 +1987,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.5uH</t>
+          <t>6.8uH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>L_Bourns-SRN4018</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2014,14 +2002,18 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.5uH SRN4018 Isat&gt;=4A</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>TDK MLZ2012N6R8LT000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>C82157</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
           <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
@@ -2036,7 +2028,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1uH</t>
+          <t>1.5uH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2055,7 +2047,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1uH SRN4018 Isat&gt;=5A</t>
+          <t>1.5uH SRN4018 Isat&gt;=4A</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2068,87 +2060,91 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>二极管</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ESD 3.3V/0.6pF</t>
+          <t>1uH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>L_Bourns-SRN4018</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>C2830293</t>
-        </is>
-      </c>
+          <t>1uH SRN4018 Isat&gt;=5A</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>低结电容 ESD 管（≤0.6pF）</t>
+          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>保险丝</t>
+          <t>二极管</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>ESD 3.3V/0.6pF</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>金瑞 JK-SMD0805-020-30V</t>
+          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C516070</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
+          <t>C2830293</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>低结电容 ESD 管（≤0.6pF）</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>三极管/MOS</t>
+          <t>保险丝</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>6V/200mA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2158,12 +2154,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>UMW AO3401A</t>
+          <t>金瑞 JK-SMD0805-020-30V</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>C347476</t>
+          <t>C516070</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2176,7 +2172,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SY7069</t>
+          <t>AO3401A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2187,16 +2183,16 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SY7069ADC</t>
+          <t>UMW AO3401A</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>淘宝（立创未见）</t>
+          <t>C347476</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2204,32 +2200,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>三极管/MOS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>SY7069</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SOT-363/SC-70-6</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>信路达 XA17-G4K</t>
+          <t>SY7069ADC</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C513494</t>
+          <t>淘宝（立创未见）</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2237,28 +2233,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CH224K</t>
+          <t>XA17-G4K</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CH224K_ESSOP-10</t>
+          <t>SOT-363/SC-70-6</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>信路达 XA17-G4K</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C970725</t>
+          <t>C513494</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P BAT</t>
+          <t>CH224K</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
+          <t>CH224K_ESSOP-10</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2284,12 +2284,12 @@
       <c r="F54" t="n">
         <v>3</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>MX1.25 卧贴 1.25WT-2P</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>C970725</t>
+        </is>
+      </c>
       <c r="I54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>103AT-2 10k NTC</t>
+          <t>MX1.25WT-2P BAT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NTC_103AT-2_Leaded_P2.54mm</t>
+          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>103AT-2 10k NTC B=3435</t>
+          <t>MX1.25 卧贴 1.25WT-2P</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>

--- a/hardware/expansion-board-v4/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v4/BOM_采购清单.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10uF</t>
+          <t>12pF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -895,20 +895,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>X5R</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>C0G/NP0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50V</t>
+        </is>
+      </c>
       <c r="F12" t="n">
         <v>50</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0603 10uF 16V X5R</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>建议 C0G（X7R 可用，需实测频偏）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -918,7 +922,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12pF</t>
+          <t>15pF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -955,7 +959,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15pF</t>
+          <t>1nF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C0G/NP0</t>
+          <t>不限</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -978,11 +982,7 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>建议 C0G（X7R 可用，需实测频偏）</t>
-        </is>
-      </c>
+      <c r="I14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1nF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>不限</t>
+          <t>X5R</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50V</t>
+          <t>25V</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>200pF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>X5R</t>
+          <t>不限</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25V</t>
+          <t>50V</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>200pF</t>
+          <t>3pF</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3pF</t>
+          <t>4.7uF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1101,19 +1101,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>不限</t>
+          <t>X5R</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50V</t>
+          <t>16V</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>50</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Samsung CL10A475KO8NNNC</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>C19666</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1124,7 +1132,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>47nF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1134,12 +1142,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>X5R</t>
+          <t>X7R</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16V</t>
+          <t>50V</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1147,14 +1155,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Samsung CL10A475KO8NNNC</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>C19666</t>
-        </is>
-      </c>
+          <t>0603 47nF 25V X7R</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1165,32 +1169,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>47nF</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>X7R</t>
+          <t>X5R</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>50V</t>
+          <t>25V</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>50</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0603 47nF 25V X7R</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6.8uF</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1215,15 +1215,15 @@
           <t>X5R</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>16V</t>
+        </is>
+      </c>
       <c r="F21" t="n">
         <v>50</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0603 6.8uF 25V X5R</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10uF</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1248,15 +1248,15 @@
           <t>X5R</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>25V</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>50</v>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1206 22uF 10V X5R</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22uF</t>
+          <t>6.8uF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1281,50 +1281,46 @@
           <t>X5R</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>16V</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
         <v>50</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1206 6.8uF 25V X5R</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>电容</t>
+          <t>电阻</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22uF</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>X5R</t>
-        </is>
-      </c>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>50</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1206 22uF 10V X5R</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>精度 ±1%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1334,7 +1330,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>52.3R</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1347,8 +1343,16 @@
       <c r="F25" t="n">
         <v>100</v>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>YAGEO RC0402FR-0752R3L ±1%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>C273696</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
           <t>精度 ±1%</t>
@@ -1363,34 +1367,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>52.3R</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>100</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>YAGEO RC0402FR-0752R3L ±1%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>C273696</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>精度 ±1%</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1400,7 +1396,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0R</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1408,11 +1404,7 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>不限</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
         <v>50</v>
@@ -1429,7 +1421,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1454,7 +1446,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>150k</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1467,7 +1459,11 @@
       <c r="F29" t="n">
         <v>50</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0603 150k 1%</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
     </row>
@@ -1479,7 +1475,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>150k</t>
+          <t>180R</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1494,7 +1490,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0603 150k 1%</t>
+          <t>0603 180R 1%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1508,7 +1504,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>180R</t>
+          <t>18k</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1521,11 +1517,7 @@
       <c r="F31" t="n">
         <v>50</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0603 180R 1%</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
     </row>
@@ -1537,7 +1529,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1562,7 +1554,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>27R</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1587,7 +1579,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27R</t>
+          <t>31.6k</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1600,7 +1592,11 @@
       <c r="F34" t="n">
         <v>50</v>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0603 31.6k 1%</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
     </row>
@@ -1612,7 +1608,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>31.6k</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1625,11 +1621,7 @@
       <c r="F35" t="n">
         <v>50</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0603 31.6k 1%</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
     </row>
@@ -1641,7 +1633,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>470k</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1654,7 +1646,11 @@
       <c r="F36" t="n">
         <v>50</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0603 470k 1%</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
     </row>
@@ -1666,7 +1662,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>470k</t>
+          <t>5.1k</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1679,11 +1675,7 @@
       <c r="F37" t="n">
         <v>50</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0603 470k 1%</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
     </row>

--- a/hardware/expansion-board-v4/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v4/BOM_采购清单.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1384,7 +1384,11 @@
       <c r="F26" t="n">
         <v>50</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>默认0R直通；调试时换值</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
     </row>
@@ -1504,7 +1508,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1529,7 +1533,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>27R</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1554,7 +1558,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27R</t>
+          <t>31.6k</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,7 +1571,11 @@
       <c r="F33" t="n">
         <v>50</v>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0603 31.6k 1%</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
     </row>
@@ -1579,7 +1587,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31.6k</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1592,11 +1600,7 @@
       <c r="F34" t="n">
         <v>50</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0603 31.6k 1%</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
     </row>
@@ -1608,7 +1612,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>470k</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1621,7 +1625,11 @@
       <c r="F35" t="n">
         <v>50</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0603 470k 1%</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
     </row>
@@ -1633,7 +1641,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>470k</t>
+          <t>5.1k</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1646,11 +1654,7 @@
       <c r="F36" t="n">
         <v>50</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0603 470k 1%</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
     </row>
@@ -1662,7 +1666,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5.1k</t>
+          <t>5.62k</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1675,7 +1679,11 @@
       <c r="F37" t="n">
         <v>50</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0603 5.62k 1%</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
     </row>
@@ -1687,7 +1695,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5.62k</t>
+          <t>6.8k</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1702,7 +1710,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0603 5.62k 1%</t>
+          <t>0603 6.8k 1%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1716,7 +1724,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6.8k</t>
+          <t>NCP18XH103F03RB 10k NTC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1731,7 +1739,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0603 6.8k 1%</t>
+          <t>Murata NCP18XH103F03RB / TDK NTCG163JF103FT1 / 国产 0603 10K 1%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1740,31 +1748,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>电阻</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NCP18XH103F03RB 10k NTC</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>绕线</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Murata NCP18XH103F03RB / TDK NTCG163JF103FT1 / 国产 0603 10K 1%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
+          <t>DDY WI0402IFR10KST-HF</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>C18221115</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>必须绕线电感，叠层款不行</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1774,7 +1794,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>27nH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1793,12 +1813,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DDY WI0402IFR10KST-HF</t>
+          <t>muRata LQW15AN27NG0ZD</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C18221115</t>
+          <t>C7519921</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1815,7 +1835,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27nH</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1834,12 +1854,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>muRata LQW15AN27NG0ZD</t>
+          <t>APV AHW1005C-33NJTF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C7519921</t>
+          <t>C6807986</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1856,7 +1876,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>6.8nH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1875,12 +1895,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>APV AHW1005C-33NJTF</t>
+          <t>muRata LQW15AN6N8G00D</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C6807986</t>
+          <t>C82919</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1897,7 +1917,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1916,12 +1936,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>muRata LQW15AN6N8G00D</t>
+          <t>muRata LQW15AN7N5G00D</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C82919</t>
+          <t>C82918</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1938,36 +1958,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>6.8uH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>绕线</t>
+          <t>不限</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>muRata LQW15AN7N5G00D</t>
+          <t>TDK MLZ2012N6R8LT000</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>C82918</t>
+          <t>C82157</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>必须绕线电感，叠层款不行</t>
+          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1999,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6.8uH</t>
+          <t>1.5uH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>L_Bourns-SRN4018</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1994,18 +2014,14 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TDK MLZ2012N6R8LT000</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>C82157</t>
-        </is>
-      </c>
+          <t>1.5uH SRN4018 Isat&gt;=4A</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
           <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
@@ -2020,7 +2036,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.5uH</t>
+          <t>1uH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2039,7 +2055,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.5uH SRN4018 Isat&gt;=4A</t>
+          <t>1uH SRN4018 Isat&gt;=5A</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2052,91 +2068,87 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>电感</t>
+          <t>二极管</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1uH</t>
+          <t>ESD 3.3V/0.6pF</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L_Bourns-SRN4018</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>不限</t>
-        </is>
-      </c>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1uH SRN4018 Isat&gt;=5A</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>C2830293</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
+          <t>低结电容 ESD 管（≤0.6pF）</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>二极管</t>
+          <t>保险丝</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ESD 3.3V/0.6pF</t>
+          <t>6V/200mA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
+          <t>金瑞 JK-SMD0805-020-30V</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C2830293</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>低结电容 ESD 管（≤0.6pF）</t>
-        </is>
-      </c>
+          <t>C516070</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>保险丝</t>
+          <t>三极管/MOS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>AO3401A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2146,12 +2158,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>金瑞 JK-SMD0805-020-30V</t>
+          <t>UMW AO3401A</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>C516070</t>
+          <t>C347476</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2164,7 +2176,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>SY7069</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2175,16 +2187,16 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>UMW AO3401A</t>
+          <t>SY7069ADC</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>C347476</t>
+          <t>淘宝（立创未见）</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2192,32 +2204,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>三极管/MOS</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SY7069</t>
+          <t>XA17-G4K</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>SOT-363/SC-70-6</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SY7069ADC</t>
+          <t>信路达 XA17-G4K</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>淘宝（立创未见）</t>
+          <t>C513494</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2225,32 +2237,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>CH224K</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SOT-363/SC-70-6</t>
+          <t>CH224K_ESSOP-10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>4</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>信路达 XA17-G4K</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C513494</t>
+          <t>C970725</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2263,12 +2271,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CH224K</t>
+          <t>MX1.25WT-2P BAT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CH224K_ESSOP-10</t>
+          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2276,12 +2284,12 @@
       <c r="F54" t="n">
         <v>3</v>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>C970725</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>MX1.25 卧贴 1.25WT-2P</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2292,12 +2300,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P BAT</t>
+          <t>SY6970</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2307,44 +2315,15 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MX1.25 卧贴 1.25WT-2P</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>SY6970QCC</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>C5357542</t>
+        </is>
+      </c>
       <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SY6970</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>SY6970QCC</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>C5357542</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hardware/expansion-board-v4/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v4/BOM_采购清单.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="采购清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
